--- a/docs/StructureDefinition-DebtPortalPayments.xlsx
+++ b/docs/StructureDefinition-DebtPortalPayments.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.348</t>
+    <t>0.66.354</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-15T08:33:43+00:00</t>
+    <t>2024-09-19T08:45:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -506,12 +506,6 @@
     <t>va-tn</t>
   </si>
   <si>
-    <t>1978: source value from AR TRANSACTION - TRANSACTION NUMBER (433-.01)</t>
-  </si>
-  <si>
-    <t>IB.ARTransaction.TransactionNumber</t>
-  </si>
-  <si>
     <t>PaymentReconciliation.identifier:va-tn.id</t>
   </si>
   <si>
@@ -738,6 +732,12 @@
     <t>Identifier.value</t>
   </si>
   <si>
+    <t>1978: source value from AR TRANSACTION - TRANSACTION NUMBER (433-.01)</t>
+  </si>
+  <si>
+    <t>IB.ARTransaction.TransactionNumber</t>
+  </si>
+  <si>
     <t>II.extension or II.root if system indicates OID or GUID (Or Role.id.extension or root)</t>
   </si>
   <si>
@@ -794,46 +794,46 @@
     <t>va-bn</t>
   </si>
   <si>
+    <t>PaymentReconciliation.identifier:va-bn.id</t>
+  </si>
+  <si>
+    <t>PaymentReconciliation.identifier:va-bn.extension</t>
+  </si>
+  <si>
+    <t>PaymentReconciliation.identifier:va-bn.use</t>
+  </si>
+  <si>
+    <t>PaymentReconciliation.identifier:va-bn.type</t>
+  </si>
+  <si>
+    <t>PaymentReconciliation.identifier:va-bn.type.id</t>
+  </si>
+  <si>
+    <t>PaymentReconciliation.identifier:va-bn.type.extension</t>
+  </si>
+  <si>
+    <t>PaymentReconciliation.identifier:va-bn.type.coding</t>
+  </si>
+  <si>
+    <t>PaymentReconciliation.identifier:va-bn.type.text</t>
+  </si>
+  <si>
+    <t>Bill Number</t>
+  </si>
+  <si>
+    <t>1979-1: fixed value = Bill Number</t>
+  </si>
+  <si>
+    <t>PaymentReconciliation.identifier:va-bn.system</t>
+  </si>
+  <si>
+    <t>PaymentReconciliation.identifier:va-bn.value</t>
+  </si>
+  <si>
     <t>1979: source value from AR TRANSACTION - BILL NUMBER (433-.03)</t>
   </si>
   <si>
     <t>IB.ARTransaction.AccountsReceivableIEN,IB.ARTransaction.PatientIEN,IB.ARTransactionComment.PatientIEN,IB.ARTransactionDescription.PatientIEN,IB.ARTransactionFiscalYear.PatientIEN</t>
-  </si>
-  <si>
-    <t>PaymentReconciliation.identifier:va-bn.id</t>
-  </si>
-  <si>
-    <t>PaymentReconciliation.identifier:va-bn.extension</t>
-  </si>
-  <si>
-    <t>PaymentReconciliation.identifier:va-bn.use</t>
-  </si>
-  <si>
-    <t>PaymentReconciliation.identifier:va-bn.type</t>
-  </si>
-  <si>
-    <t>PaymentReconciliation.identifier:va-bn.type.id</t>
-  </si>
-  <si>
-    <t>PaymentReconciliation.identifier:va-bn.type.extension</t>
-  </si>
-  <si>
-    <t>PaymentReconciliation.identifier:va-bn.type.coding</t>
-  </si>
-  <si>
-    <t>PaymentReconciliation.identifier:va-bn.type.text</t>
-  </si>
-  <si>
-    <t>Bill Number</t>
-  </si>
-  <si>
-    <t>1979-1: fixed value = Bill Number</t>
-  </si>
-  <si>
-    <t>PaymentReconciliation.identifier:va-bn.system</t>
-  </si>
-  <si>
-    <t>PaymentReconciliation.identifier:va-bn.value</t>
   </si>
   <si>
     <t>PaymentReconciliation.identifier:va-bn.period</t>
@@ -3395,7 +3395,7 @@
         <v>89</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="I12" t="s" s="2">
         <v>79</v>
@@ -3478,10 +3478,10 @@
         <v>101</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>157</v>
+        <v>79</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>158</v>
+        <v>79</v>
       </c>
       <c r="AM12" t="s" s="2">
         <v>153</v>
@@ -3498,10 +3498,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3524,13 +3524,13 @@
         <v>79</v>
       </c>
       <c r="K13" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="L13" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="M13" t="s" s="2">
         <v>161</v>
-      </c>
-      <c r="L13" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="M13" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -3581,7 +3581,7 @@
         <v>79</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
@@ -3611,15 +3611,15 @@
         <v>79</v>
       </c>
       <c r="AP13" t="s" s="2">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3648,7 +3648,7 @@
         <v>136</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="N14" t="s" s="2">
         <v>138</v>
@@ -3689,10 +3689,10 @@
         <v>79</v>
       </c>
       <c r="AB14" t="s" s="2">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="AC14" t="s" s="2">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="AD14" t="s" s="2">
         <v>79</v>
@@ -3701,7 +3701,7 @@
         <v>152</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>80</v>
@@ -3731,15 +3731,15 @@
         <v>79</v>
       </c>
       <c r="AP14" t="s" s="2">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3765,16 +3765,16 @@
         <v>109</v>
       </c>
       <c r="L15" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="M15" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="N15" t="s" s="2">
         <v>174</v>
       </c>
-      <c r="M15" t="s" s="2">
+      <c r="O15" t="s" s="2">
         <v>175</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="O15" t="s" s="2">
-        <v>177</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>79</v>
@@ -3799,31 +3799,31 @@
         <v>79</v>
       </c>
       <c r="X15" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="Y15" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="Z15" t="s" s="2">
         <v>178</v>
       </c>
-      <c r="Y15" t="s" s="2">
+      <c r="AA15" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB15" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC15" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD15" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE15" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF15" t="s" s="2">
         <v>179</v>
-      </c>
-      <c r="Z15" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="AA15" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB15" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC15" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD15" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE15" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF15" t="s" s="2">
-        <v>181</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
@@ -3853,15 +3853,15 @@
         <v>79</v>
       </c>
       <c r="AP15" t="s" s="2">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3884,19 +3884,19 @@
         <v>90</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="L16" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="M16" t="s" s="2">
         <v>185</v>
       </c>
-      <c r="L16" t="s" s="2">
+      <c r="N16" t="s" s="2">
         <v>186</v>
       </c>
-      <c r="M16" t="s" s="2">
+      <c r="O16" t="s" s="2">
         <v>187</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="O16" t="s" s="2">
-        <v>189</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>79</v>
@@ -3921,31 +3921,31 @@
         <v>79</v>
       </c>
       <c r="X16" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="Y16" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="Z16" t="s" s="2">
         <v>190</v>
       </c>
-      <c r="Y16" t="s" s="2">
+      <c r="AA16" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB16" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC16" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD16" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE16" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF16" t="s" s="2">
         <v>191</v>
-      </c>
-      <c r="Z16" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="AA16" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB16" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC16" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD16" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE16" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF16" t="s" s="2">
-        <v>193</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
@@ -3975,15 +3975,15 @@
         <v>79</v>
       </c>
       <c r="AP16" t="s" s="2">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4006,13 +4006,13 @@
         <v>79</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="L17" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="M17" t="s" s="2">
         <v>161</v>
-      </c>
-      <c r="L17" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="M17" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -4063,7 +4063,7 @@
         <v>79</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -4093,15 +4093,15 @@
         <v>79</v>
       </c>
       <c r="AP17" t="s" s="2">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4130,7 +4130,7 @@
         <v>136</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="N18" t="s" s="2">
         <v>138</v>
@@ -4171,10 +4171,10 @@
         <v>79</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>79</v>
@@ -4183,7 +4183,7 @@
         <v>152</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -4213,15 +4213,15 @@
         <v>79</v>
       </c>
       <c r="AP18" t="s" s="2">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4244,19 +4244,19 @@
         <v>90</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="L19" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="M19" t="s" s="2">
         <v>200</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="N19" t="s" s="2">
         <v>201</v>
       </c>
-      <c r="M19" t="s" s="2">
+      <c r="O19" t="s" s="2">
         <v>202</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>204</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>79</v>
@@ -4305,7 +4305,7 @@
         <v>79</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -4335,15 +4335,15 @@
         <v>79</v>
       </c>
       <c r="AP19" t="s" s="2">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4366,19 +4366,19 @@
         <v>90</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="L20" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="M20" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="N20" t="s" s="2">
         <v>209</v>
       </c>
-      <c r="M20" t="s" s="2">
+      <c r="O20" t="s" s="2">
         <v>210</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>212</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>79</v>
@@ -4388,7 +4388,7 @@
         <v>79</v>
       </c>
       <c r="S20" t="s" s="2">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="T20" t="s" s="2">
         <v>79</v>
@@ -4427,7 +4427,7 @@
         <v>79</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -4442,7 +4442,7 @@
         <v>101</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>79</v>
@@ -4457,15 +4457,15 @@
         <v>79</v>
       </c>
       <c r="AP20" t="s" s="2">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4491,16 +4491,16 @@
         <v>103</v>
       </c>
       <c r="L21" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="M21" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="N21" t="s" s="2">
         <v>219</v>
       </c>
-      <c r="M21" t="s" s="2">
+      <c r="O21" t="s" s="2">
         <v>220</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="O21" t="s" s="2">
-        <v>222</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>79</v>
@@ -4513,7 +4513,7 @@
         <v>79</v>
       </c>
       <c r="T21" t="s" s="2">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="U21" t="s" s="2">
         <v>79</v>
@@ -4549,7 +4549,7 @@
         <v>79</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -4579,15 +4579,15 @@
         <v>79</v>
       </c>
       <c r="AP21" t="s" s="2">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4601,7 +4601,7 @@
         <v>89</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>79</v>
@@ -4610,16 +4610,16 @@
         <v>90</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="L22" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="M22" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="N22" t="s" s="2">
         <v>228</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>230</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4633,7 +4633,7 @@
         <v>79</v>
       </c>
       <c r="T22" t="s" s="2">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="U22" t="s" s="2">
         <v>79</v>
@@ -4669,7 +4669,7 @@
         <v>79</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -4684,10 +4684,10 @@
         <v>101</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>79</v>
+        <v>231</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>79</v>
+        <v>232</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>79</v>
@@ -4961,7 +4961,7 @@
         <v>89</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>79</v>
@@ -5044,10 +5044,10 @@
         <v>101</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>251</v>
+        <v>79</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>252</v>
+        <v>79</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>153</v>
@@ -5064,10 +5064,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5090,13 +5090,13 @@
         <v>79</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="L26" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>161</v>
-      </c>
-      <c r="L26" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -5147,7 +5147,7 @@
         <v>79</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -5177,15 +5177,15 @@
         <v>79</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5214,7 +5214,7 @@
         <v>136</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="N27" t="s" s="2">
         <v>138</v>
@@ -5255,10 +5255,10 @@
         <v>79</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="AC27" t="s" s="2">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="AD27" t="s" s="2">
         <v>79</v>
@@ -5267,7 +5267,7 @@
         <v>152</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -5297,15 +5297,15 @@
         <v>79</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5331,16 +5331,16 @@
         <v>109</v>
       </c>
       <c r="L28" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="M28" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="N28" t="s" s="2">
         <v>174</v>
       </c>
-      <c r="M28" t="s" s="2">
+      <c r="O28" t="s" s="2">
         <v>175</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>177</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>79</v>
@@ -5365,31 +5365,31 @@
         <v>79</v>
       </c>
       <c r="X28" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="Y28" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="Z28" t="s" s="2">
         <v>178</v>
       </c>
-      <c r="Y28" t="s" s="2">
+      <c r="AA28" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB28" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC28" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD28" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE28" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF28" t="s" s="2">
         <v>179</v>
-      </c>
-      <c r="Z28" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="AA28" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB28" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC28" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD28" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE28" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF28" t="s" s="2">
-        <v>181</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5419,15 +5419,15 @@
         <v>79</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5450,19 +5450,19 @@
         <v>90</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="L29" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="M29" t="s" s="2">
         <v>185</v>
       </c>
-      <c r="L29" t="s" s="2">
+      <c r="N29" t="s" s="2">
         <v>186</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="O29" t="s" s="2">
         <v>187</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>189</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>79</v>
@@ -5487,31 +5487,31 @@
         <v>79</v>
       </c>
       <c r="X29" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="Y29" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="Z29" t="s" s="2">
         <v>190</v>
       </c>
-      <c r="Y29" t="s" s="2">
+      <c r="AA29" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB29" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC29" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD29" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE29" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF29" t="s" s="2">
         <v>191</v>
-      </c>
-      <c r="Z29" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="AA29" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB29" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC29" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD29" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE29" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF29" t="s" s="2">
-        <v>193</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5541,15 +5541,15 @@
         <v>79</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5572,13 +5572,13 @@
         <v>79</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="L30" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>161</v>
-      </c>
-      <c r="L30" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -5629,7 +5629,7 @@
         <v>79</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5659,15 +5659,15 @@
         <v>79</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5696,7 +5696,7 @@
         <v>136</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="N31" t="s" s="2">
         <v>138</v>
@@ -5737,10 +5737,10 @@
         <v>79</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="AC31" t="s" s="2">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="AD31" t="s" s="2">
         <v>79</v>
@@ -5749,7 +5749,7 @@
         <v>152</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5779,15 +5779,15 @@
         <v>79</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5810,19 +5810,19 @@
         <v>90</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="L32" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="M32" t="s" s="2">
         <v>200</v>
       </c>
-      <c r="L32" t="s" s="2">
+      <c r="N32" t="s" s="2">
         <v>201</v>
       </c>
-      <c r="M32" t="s" s="2">
+      <c r="O32" t="s" s="2">
         <v>202</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>204</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>79</v>
@@ -5871,7 +5871,7 @@
         <v>79</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -5901,15 +5901,15 @@
         <v>79</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5932,19 +5932,19 @@
         <v>90</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="L33" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="M33" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="N33" t="s" s="2">
         <v>209</v>
       </c>
-      <c r="M33" t="s" s="2">
+      <c r="O33" t="s" s="2">
         <v>210</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>212</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>79</v>
@@ -5954,7 +5954,7 @@
         <v>79</v>
       </c>
       <c r="S33" t="s" s="2">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="T33" t="s" s="2">
         <v>79</v>
@@ -5993,7 +5993,7 @@
         <v>79</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -6008,7 +6008,7 @@
         <v>101</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>79</v>
@@ -6023,15 +6023,15 @@
         <v>79</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6057,16 +6057,16 @@
         <v>103</v>
       </c>
       <c r="L34" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="M34" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="N34" t="s" s="2">
         <v>219</v>
       </c>
-      <c r="M34" t="s" s="2">
+      <c r="O34" t="s" s="2">
         <v>220</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>222</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>79</v>
@@ -6079,7 +6079,7 @@
         <v>79</v>
       </c>
       <c r="T34" t="s" s="2">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="U34" t="s" s="2">
         <v>79</v>
@@ -6115,7 +6115,7 @@
         <v>79</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -6145,15 +6145,15 @@
         <v>79</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6167,7 +6167,7 @@
         <v>89</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>79</v>
@@ -6176,16 +6176,16 @@
         <v>90</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="M35" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="N35" t="s" s="2">
         <v>228</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>230</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -6199,7 +6199,7 @@
         <v>79</v>
       </c>
       <c r="T35" t="s" s="2">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="U35" t="s" s="2">
         <v>79</v>
@@ -6235,7 +6235,7 @@
         <v>79</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6250,10 +6250,10 @@
         <v>101</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>79</v>
+        <v>263</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>79</v>
+        <v>264</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>79</v>
@@ -6571,7 +6571,7 @@
         <v>79</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="Y38" t="s" s="2">
         <v>273</v>
@@ -7295,7 +7295,7 @@
         <v>79</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="Y44" t="s" s="2">
         <v>317</v>
@@ -7380,7 +7380,7 @@
         <v>79</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="L45" t="s" s="2">
         <v>320</v>
@@ -7980,13 +7980,13 @@
         <v>79</v>
       </c>
       <c r="K50" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="L50" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>161</v>
-      </c>
-      <c r="L50" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -8037,7 +8037,7 @@
         <v>79</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -8067,7 +8067,7 @@
         <v>79</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="51" hidden="true">
@@ -8104,7 +8104,7 @@
         <v>136</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="N51" t="s" s="2">
         <v>138</v>
@@ -8157,7 +8157,7 @@
         <v>79</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8187,7 +8187,7 @@
         <v>79</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="52" hidden="true">
@@ -8580,7 +8580,7 @@
         <v>79</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="L55" t="s" s="2">
         <v>367</v>
@@ -9664,13 +9664,13 @@
         <v>79</v>
       </c>
       <c r="K64" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="M64" t="s" s="2">
         <v>161</v>
-      </c>
-      <c r="L64" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9721,7 +9721,7 @@
         <v>79</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -9751,7 +9751,7 @@
         <v>79</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="65" hidden="true">
@@ -9788,7 +9788,7 @@
         <v>136</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="N65" t="s" s="2">
         <v>138</v>
@@ -9841,7 +9841,7 @@
         <v>79</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -9871,7 +9871,7 @@
         <v>79</v>
       </c>
       <c r="AP65" t="s" s="2">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="66" hidden="true">
@@ -10264,7 +10264,7 @@
         <v>79</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="L69" t="s" s="2">
         <v>367</v>
@@ -10386,13 +10386,13 @@
         <v>79</v>
       </c>
       <c r="K70" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="L70" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="M70" t="s" s="2">
         <v>161</v>
-      </c>
-      <c r="L70" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -10443,7 +10443,7 @@
         <v>79</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10473,7 +10473,7 @@
         <v>79</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="71" hidden="true">
@@ -10510,7 +10510,7 @@
         <v>136</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="N71" t="s" s="2">
         <v>138</v>
@@ -10551,10 +10551,10 @@
         <v>79</v>
       </c>
       <c r="AB71" t="s" s="2">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="AC71" t="s" s="2">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="AD71" t="s" s="2">
         <v>79</v>
@@ -10563,7 +10563,7 @@
         <v>152</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -10593,7 +10593,7 @@
         <v>79</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="72" hidden="true">
@@ -10624,19 +10624,19 @@
         <v>90</v>
       </c>
       <c r="K72" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="L72" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="M72" t="s" s="2">
         <v>200</v>
       </c>
-      <c r="L72" t="s" s="2">
+      <c r="N72" t="s" s="2">
         <v>201</v>
       </c>
-      <c r="M72" t="s" s="2">
+      <c r="O72" t="s" s="2">
         <v>202</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="O72" t="s" s="2">
-        <v>204</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>79</v>
@@ -10685,7 +10685,7 @@
         <v>79</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -10715,7 +10715,7 @@
         <v>79</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="73" hidden="true">
@@ -10746,19 +10746,19 @@
         <v>90</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="L73" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="M73" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="N73" t="s" s="2">
         <v>209</v>
       </c>
-      <c r="M73" t="s" s="2">
+      <c r="O73" t="s" s="2">
         <v>210</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="O73" t="s" s="2">
-        <v>212</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>79</v>
@@ -10807,7 +10807,7 @@
         <v>79</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -10837,7 +10837,7 @@
         <v>79</v>
       </c>
       <c r="AP73" t="s" s="2">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="74" hidden="true">
@@ -11830,13 +11830,13 @@
         <v>79</v>
       </c>
       <c r="K82" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="L82" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="M82" t="s" s="2">
         <v>161</v>
-      </c>
-      <c r="L82" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="M82" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -11887,7 +11887,7 @@
         <v>79</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -11917,7 +11917,7 @@
         <v>79</v>
       </c>
       <c r="AP82" t="s" s="2">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="83" hidden="true">
@@ -11954,7 +11954,7 @@
         <v>136</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="N83" t="s" s="2">
         <v>138</v>
@@ -12007,7 +12007,7 @@
         <v>79</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -12037,7 +12037,7 @@
         <v>79</v>
       </c>
       <c r="AP83" t="s" s="2">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="84" hidden="true">
@@ -12430,7 +12430,7 @@
         <v>79</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="L87" t="s" s="2">
         <v>367</v>
@@ -12552,13 +12552,13 @@
         <v>79</v>
       </c>
       <c r="K88" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="L88" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="M88" t="s" s="2">
         <v>161</v>
-      </c>
-      <c r="L88" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="M88" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -12609,7 +12609,7 @@
         <v>79</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -12639,7 +12639,7 @@
         <v>79</v>
       </c>
       <c r="AP88" t="s" s="2">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="89" hidden="true">
@@ -12676,7 +12676,7 @@
         <v>136</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="N89" t="s" s="2">
         <v>138</v>
@@ -12717,10 +12717,10 @@
         <v>79</v>
       </c>
       <c r="AB89" t="s" s="2">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="AC89" t="s" s="2">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="AD89" t="s" s="2">
         <v>79</v>
@@ -12729,7 +12729,7 @@
         <v>152</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -12759,7 +12759,7 @@
         <v>79</v>
       </c>
       <c r="AP89" t="s" s="2">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="90" hidden="true">
@@ -12790,19 +12790,19 @@
         <v>90</v>
       </c>
       <c r="K90" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="L90" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="M90" t="s" s="2">
         <v>200</v>
       </c>
-      <c r="L90" t="s" s="2">
+      <c r="N90" t="s" s="2">
         <v>201</v>
       </c>
-      <c r="M90" t="s" s="2">
+      <c r="O90" t="s" s="2">
         <v>202</v>
-      </c>
-      <c r="N90" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="O90" t="s" s="2">
-        <v>204</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>79</v>
@@ -12851,7 +12851,7 @@
         <v>79</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -12881,7 +12881,7 @@
         <v>79</v>
       </c>
       <c r="AP90" t="s" s="2">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="91" hidden="true">
@@ -12912,19 +12912,19 @@
         <v>90</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="L91" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="M91" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="N91" t="s" s="2">
         <v>209</v>
       </c>
-      <c r="M91" t="s" s="2">
+      <c r="O91" t="s" s="2">
         <v>210</v>
-      </c>
-      <c r="N91" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="O91" t="s" s="2">
-        <v>212</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>79</v>
@@ -12973,7 +12973,7 @@
         <v>79</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -13003,7 +13003,7 @@
         <v>79</v>
       </c>
       <c r="AP91" t="s" s="2">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="92" hidden="true">
@@ -13996,13 +13996,13 @@
         <v>79</v>
       </c>
       <c r="K100" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="L100" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="M100" t="s" s="2">
         <v>161</v>
-      </c>
-      <c r="L100" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="M100" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -14053,7 +14053,7 @@
         <v>79</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -14083,7 +14083,7 @@
         <v>79</v>
       </c>
       <c r="AP100" t="s" s="2">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="101" hidden="true">
@@ -14120,7 +14120,7 @@
         <v>136</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="N101" t="s" s="2">
         <v>138</v>
@@ -14173,7 +14173,7 @@
         <v>79</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
@@ -14203,7 +14203,7 @@
         <v>79</v>
       </c>
       <c r="AP101" t="s" s="2">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="102" hidden="true">
@@ -14596,7 +14596,7 @@
         <v>79</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="L105" t="s" s="2">
         <v>367</v>
@@ -14718,13 +14718,13 @@
         <v>79</v>
       </c>
       <c r="K106" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="L106" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="M106" t="s" s="2">
         <v>161</v>
-      </c>
-      <c r="L106" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="M106" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" s="2"/>
@@ -14775,7 +14775,7 @@
         <v>79</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -14805,7 +14805,7 @@
         <v>79</v>
       </c>
       <c r="AP106" t="s" s="2">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="107" hidden="true">
@@ -14842,7 +14842,7 @@
         <v>136</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="N107" t="s" s="2">
         <v>138</v>
@@ -14883,10 +14883,10 @@
         <v>79</v>
       </c>
       <c r="AB107" t="s" s="2">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="AC107" t="s" s="2">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="AD107" t="s" s="2">
         <v>79</v>
@@ -14895,7 +14895,7 @@
         <v>152</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
@@ -14925,7 +14925,7 @@
         <v>79</v>
       </c>
       <c r="AP107" t="s" s="2">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="108" hidden="true">
@@ -14956,19 +14956,19 @@
         <v>90</v>
       </c>
       <c r="K108" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="L108" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="M108" t="s" s="2">
         <v>200</v>
       </c>
-      <c r="L108" t="s" s="2">
+      <c r="N108" t="s" s="2">
         <v>201</v>
       </c>
-      <c r="M108" t="s" s="2">
+      <c r="O108" t="s" s="2">
         <v>202</v>
-      </c>
-      <c r="N108" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="O108" t="s" s="2">
-        <v>204</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>79</v>
@@ -15017,7 +15017,7 @@
         <v>79</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -15047,7 +15047,7 @@
         <v>79</v>
       </c>
       <c r="AP108" t="s" s="2">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="109" hidden="true">
@@ -15078,19 +15078,19 @@
         <v>90</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="L109" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="M109" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="N109" t="s" s="2">
         <v>209</v>
       </c>
-      <c r="M109" t="s" s="2">
+      <c r="O109" t="s" s="2">
         <v>210</v>
-      </c>
-      <c r="N109" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="O109" t="s" s="2">
-        <v>212</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>79</v>
@@ -15139,7 +15139,7 @@
         <v>79</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
@@ -15169,7 +15169,7 @@
         <v>79</v>
       </c>
       <c r="AP109" t="s" s="2">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="110" hidden="true">
@@ -16162,13 +16162,13 @@
         <v>79</v>
       </c>
       <c r="K118" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="L118" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="M118" t="s" s="2">
         <v>161</v>
-      </c>
-      <c r="L118" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="M118" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="N118" s="2"/>
       <c r="O118" s="2"/>
@@ -16219,7 +16219,7 @@
         <v>79</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>80</v>
@@ -16249,7 +16249,7 @@
         <v>79</v>
       </c>
       <c r="AP118" t="s" s="2">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="119" hidden="true">
@@ -16286,7 +16286,7 @@
         <v>136</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="N119" t="s" s="2">
         <v>138</v>
@@ -16339,7 +16339,7 @@
         <v>79</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>80</v>
@@ -16369,7 +16369,7 @@
         <v>79</v>
       </c>
       <c r="AP119" t="s" s="2">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="120" hidden="true">
@@ -16762,7 +16762,7 @@
         <v>79</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="L123" t="s" s="2">
         <v>367</v>
@@ -16884,13 +16884,13 @@
         <v>79</v>
       </c>
       <c r="K124" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="L124" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="M124" t="s" s="2">
         <v>161</v>
-      </c>
-      <c r="L124" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="M124" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="N124" s="2"/>
       <c r="O124" s="2"/>
@@ -16941,7 +16941,7 @@
         <v>79</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>80</v>
@@ -16971,7 +16971,7 @@
         <v>79</v>
       </c>
       <c r="AP124" t="s" s="2">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="125" hidden="true">
@@ -17008,7 +17008,7 @@
         <v>136</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="N125" t="s" s="2">
         <v>138</v>
@@ -17049,10 +17049,10 @@
         <v>79</v>
       </c>
       <c r="AB125" t="s" s="2">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="AC125" t="s" s="2">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="AD125" t="s" s="2">
         <v>79</v>
@@ -17061,7 +17061,7 @@
         <v>152</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>80</v>
@@ -17091,7 +17091,7 @@
         <v>79</v>
       </c>
       <c r="AP125" t="s" s="2">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="126" hidden="true">
@@ -17122,19 +17122,19 @@
         <v>90</v>
       </c>
       <c r="K126" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="L126" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="M126" t="s" s="2">
         <v>200</v>
       </c>
-      <c r="L126" t="s" s="2">
+      <c r="N126" t="s" s="2">
         <v>201</v>
       </c>
-      <c r="M126" t="s" s="2">
+      <c r="O126" t="s" s="2">
         <v>202</v>
-      </c>
-      <c r="N126" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="O126" t="s" s="2">
-        <v>204</v>
       </c>
       <c r="P126" t="s" s="2">
         <v>79</v>
@@ -17183,7 +17183,7 @@
         <v>79</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>80</v>
@@ -17213,7 +17213,7 @@
         <v>79</v>
       </c>
       <c r="AP126" t="s" s="2">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="127" hidden="true">
@@ -17244,19 +17244,19 @@
         <v>90</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="L127" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="M127" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="N127" t="s" s="2">
         <v>209</v>
       </c>
-      <c r="M127" t="s" s="2">
+      <c r="O127" t="s" s="2">
         <v>210</v>
-      </c>
-      <c r="N127" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="O127" t="s" s="2">
-        <v>212</v>
       </c>
       <c r="P127" t="s" s="2">
         <v>79</v>
@@ -17305,7 +17305,7 @@
         <v>79</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>80</v>
@@ -17335,7 +17335,7 @@
         <v>79</v>
       </c>
       <c r="AP127" t="s" s="2">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="128" hidden="true">
@@ -18328,13 +18328,13 @@
         <v>79</v>
       </c>
       <c r="K136" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="L136" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="M136" t="s" s="2">
         <v>161</v>
-      </c>
-      <c r="L136" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="M136" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="N136" s="2"/>
       <c r="O136" s="2"/>
@@ -18385,7 +18385,7 @@
         <v>79</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>80</v>
@@ -18415,7 +18415,7 @@
         <v>79</v>
       </c>
       <c r="AP136" t="s" s="2">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="137" hidden="true">
@@ -18452,7 +18452,7 @@
         <v>136</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="N137" t="s" s="2">
         <v>138</v>
@@ -18505,7 +18505,7 @@
         <v>79</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>80</v>
@@ -18535,7 +18535,7 @@
         <v>79</v>
       </c>
       <c r="AP137" t="s" s="2">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="138" hidden="true">
@@ -18928,7 +18928,7 @@
         <v>79</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="L141" t="s" s="2">
         <v>367</v>
@@ -19050,13 +19050,13 @@
         <v>79</v>
       </c>
       <c r="K142" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="L142" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="M142" t="s" s="2">
         <v>161</v>
-      </c>
-      <c r="L142" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="M142" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="N142" s="2"/>
       <c r="O142" s="2"/>
@@ -19107,7 +19107,7 @@
         <v>79</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>80</v>
@@ -19137,7 +19137,7 @@
         <v>79</v>
       </c>
       <c r="AP142" t="s" s="2">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="143" hidden="true">
@@ -19174,7 +19174,7 @@
         <v>136</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="N143" t="s" s="2">
         <v>138</v>
@@ -19215,10 +19215,10 @@
         <v>79</v>
       </c>
       <c r="AB143" t="s" s="2">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="AC143" t="s" s="2">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="AD143" t="s" s="2">
         <v>79</v>
@@ -19227,7 +19227,7 @@
         <v>152</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>80</v>
@@ -19257,7 +19257,7 @@
         <v>79</v>
       </c>
       <c r="AP143" t="s" s="2">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="144" hidden="true">
@@ -19288,19 +19288,19 @@
         <v>90</v>
       </c>
       <c r="K144" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="L144" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="M144" t="s" s="2">
         <v>200</v>
       </c>
-      <c r="L144" t="s" s="2">
+      <c r="N144" t="s" s="2">
         <v>201</v>
       </c>
-      <c r="M144" t="s" s="2">
+      <c r="O144" t="s" s="2">
         <v>202</v>
-      </c>
-      <c r="N144" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="O144" t="s" s="2">
-        <v>204</v>
       </c>
       <c r="P144" t="s" s="2">
         <v>79</v>
@@ -19349,7 +19349,7 @@
         <v>79</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>80</v>
@@ -19379,7 +19379,7 @@
         <v>79</v>
       </c>
       <c r="AP144" t="s" s="2">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="145" hidden="true">
@@ -19410,19 +19410,19 @@
         <v>90</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="L145" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="M145" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="N145" t="s" s="2">
         <v>209</v>
       </c>
-      <c r="M145" t="s" s="2">
+      <c r="O145" t="s" s="2">
         <v>210</v>
-      </c>
-      <c r="N145" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="O145" t="s" s="2">
-        <v>212</v>
       </c>
       <c r="P145" t="s" s="2">
         <v>79</v>
@@ -19471,7 +19471,7 @@
         <v>79</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>80</v>
@@ -19501,7 +19501,7 @@
         <v>79</v>
       </c>
       <c r="AP145" t="s" s="2">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="146" hidden="true">
@@ -20372,7 +20372,7 @@
         <v>79</v>
       </c>
       <c r="K153" t="s" s="2">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="L153" t="s" s="2">
         <v>522</v>
@@ -20614,13 +20614,13 @@
         <v>79</v>
       </c>
       <c r="K155" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="L155" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="M155" t="s" s="2">
         <v>161</v>
-      </c>
-      <c r="L155" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="M155" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="N155" s="2"/>
       <c r="O155" s="2"/>
@@ -20671,7 +20671,7 @@
         <v>79</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>80</v>
@@ -20701,7 +20701,7 @@
         <v>79</v>
       </c>
       <c r="AP155" t="s" s="2">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="156" hidden="true">
@@ -20738,7 +20738,7 @@
         <v>136</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="N156" t="s" s="2">
         <v>138</v>
@@ -20791,7 +20791,7 @@
         <v>79</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>80</v>
@@ -20821,7 +20821,7 @@
         <v>79</v>
       </c>
       <c r="AP156" t="s" s="2">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="157" hidden="true">
@@ -21009,7 +21009,7 @@
         <v>79</v>
       </c>
       <c r="X158" t="s" s="2">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="Y158" t="s" s="2">
         <v>539</v>
@@ -21094,7 +21094,7 @@
         <v>79</v>
       </c>
       <c r="K159" t="s" s="2">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="L159" t="s" s="2">
         <v>542</v>

--- a/docs/StructureDefinition-DebtPortalPayments.xlsx
+++ b/docs/StructureDefinition-DebtPortalPayments.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.354</t>
+    <t>0.66.364</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-19T08:45:12+00:00</t>
+    <t>2024-10-02T18:53:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalPayments.xlsx
+++ b/docs/StructureDefinition-DebtPortalPayments.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.364</t>
+    <t>0.66.366</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-02T18:53:29+00:00</t>
+    <t>2024-10-11T07:57:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalPayments.xlsx
+++ b/docs/StructureDefinition-DebtPortalPayments.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.366</t>
+    <t>0.66.367</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-11T07:57:28+00:00</t>
+    <t>2024-10-13T09:59:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalPayments.xlsx
+++ b/docs/StructureDefinition-DebtPortalPayments.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.367</t>
+    <t>0.67.369</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-13T09:59:39+00:00</t>
+    <t>2024-10-18T16:05:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalPayments.xlsx
+++ b/docs/StructureDefinition-DebtPortalPayments.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.369</t>
+    <t>0.67.370</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-18T16:05:33+00:00</t>
+    <t>2024-10-20T09:02:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalPayments.xlsx
+++ b/docs/StructureDefinition-DebtPortalPayments.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.370</t>
+    <t>0.67.378</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-20T09:02:32+00:00</t>
+    <t>2024-10-30T12:26:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalPayments.xlsx
+++ b/docs/StructureDefinition-DebtPortalPayments.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.378</t>
+    <t>0.67.381</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-30T12:26:51+00:00</t>
+    <t>2024-11-03T11:50:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1333,7 +1333,7 @@
     <t>PaymentReconciliation.detail:va-principal-collected.amount</t>
   </si>
   <si>
-    <t>1986: source value from AR TRANSACTION - PRIN. COLLECTED (433-31)</t>
+    <t>1986: source value from AR TRANSACTION - PRIN.COLLECTED (433-31)</t>
   </si>
   <si>
     <t>IB.ARTransaction.PrincipaAmountCollected</t>
@@ -1471,7 +1471,7 @@
     <t>PaymentReconciliation.detail:va-admin-collected.amount</t>
   </si>
   <si>
-    <t>1988: source value from AR TRANSACTION - ADMIN. COLLECTED (433-33)</t>
+    <t>1988: source value from AR TRANSACTION - ADMIN.COLLECTED (433-33)</t>
   </si>
   <si>
     <t>IB.ARTransaction.AdministrativeAmountCollected</t>

--- a/docs/StructureDefinition-DebtPortalPayments.xlsx
+++ b/docs/StructureDefinition-DebtPortalPayments.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6107" uniqueCount="546">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6107" uniqueCount="545">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.381</t>
+    <t>0.68.397</t>
   </si>
   <si>
     <t>Name</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-03T11:50:46+00:00</t>
+    <t>2024-11-10T10:13:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -855,9 +855,6 @@
   </si>
   <si>
     <t>Need to track the status of the resource as 'draft' resources may undergo further edits while 'active' resources are immutable and may only have their status changed to 'cancelled'.</t>
-  </si>
-  <si>
-    <t>active</t>
   </si>
   <si>
     <t>A code specifying the state of the resource instance.</t>
@@ -6556,7 +6553,7 @@
         <v>79</v>
       </c>
       <c r="S38" t="s" s="2">
-        <v>272</v>
+        <v>11</v>
       </c>
       <c r="T38" t="s" s="2">
         <v>79</v>
@@ -6574,10 +6571,10 @@
         <v>176</v>
       </c>
       <c r="Y38" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="Z38" t="s" s="2">
         <v>273</v>
-      </c>
-      <c r="Z38" t="s" s="2">
-        <v>274</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>79</v>
@@ -6610,16 +6607,16 @@
         <v>101</v>
       </c>
       <c r="AK38" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="AL38" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM38" t="s" s="2">
         <v>275</v>
       </c>
-      <c r="AL38" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM38" t="s" s="2">
+      <c r="AN38" t="s" s="2">
         <v>276</v>
-      </c>
-      <c r="AN38" t="s" s="2">
-        <v>277</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>79</v>
@@ -6630,10 +6627,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6659,14 +6656,14 @@
         <v>236</v>
       </c>
       <c r="L39" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="M39" t="s" s="2">
         <v>279</v>
-      </c>
-      <c r="M39" t="s" s="2">
-        <v>280</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>79</v>
@@ -6715,7 +6712,7 @@
         <v>79</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6739,7 +6736,7 @@
         <v>79</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>79</v>
@@ -6750,10 +6747,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6776,17 +6773,17 @@
         <v>90</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="L40" t="s" s="2">
         <v>284</v>
       </c>
-      <c r="L40" t="s" s="2">
+      <c r="M40" t="s" s="2">
         <v>285</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>286</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>79</v>
@@ -6835,7 +6832,7 @@
         <v>79</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>89</v>
@@ -6850,16 +6847,16 @@
         <v>101</v>
       </c>
       <c r="AK40" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="AL40" t="s" s="2">
         <v>288</v>
       </c>
-      <c r="AL40" t="s" s="2">
+      <c r="AM40" t="s" s="2">
         <v>289</v>
       </c>
-      <c r="AM40" t="s" s="2">
+      <c r="AN40" t="s" s="2">
         <v>290</v>
-      </c>
-      <c r="AN40" t="s" s="2">
-        <v>291</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>79</v>
@@ -6870,10 +6867,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6899,16 +6896,16 @@
         <v>243</v>
       </c>
       <c r="L41" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="M41" t="s" s="2">
         <v>293</v>
       </c>
-      <c r="M41" t="s" s="2">
+      <c r="N41" t="s" s="2">
         <v>294</v>
       </c>
-      <c r="N41" t="s" s="2">
+      <c r="O41" t="s" s="2">
         <v>295</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>296</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>79</v>
@@ -6957,7 +6954,7 @@
         <v>79</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -6978,10 +6975,10 @@
         <v>79</v>
       </c>
       <c r="AM41" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="AN41" t="s" s="2">
         <v>297</v>
-      </c>
-      <c r="AN41" t="s" s="2">
-        <v>298</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>79</v>
@@ -6992,10 +6989,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7018,17 +7015,17 @@
         <v>79</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="L42" t="s" s="2">
         <v>300</v>
       </c>
-      <c r="L42" t="s" s="2">
+      <c r="M42" t="s" s="2">
         <v>301</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>302</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>79</v>
@@ -7077,7 +7074,7 @@
         <v>79</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -7101,10 +7098,10 @@
         <v>79</v>
       </c>
       <c r="AN42" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="AO42" t="s" s="2">
         <v>304</v>
-      </c>
-      <c r="AO42" t="s" s="2">
-        <v>305</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>79</v>
@@ -7112,10 +7109,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7138,17 +7135,17 @@
         <v>79</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="L43" t="s" s="2">
         <v>307</v>
       </c>
-      <c r="L43" t="s" s="2">
+      <c r="M43" t="s" s="2">
         <v>308</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>309</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>79</v>
@@ -7197,7 +7194,7 @@
         <v>79</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7224,7 +7221,7 @@
         <v>79</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>79</v>
@@ -7232,10 +7229,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7261,16 +7258,16 @@
         <v>109</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>313</v>
       </c>
-      <c r="M44" t="s" s="2">
+      <c r="N44" t="s" s="2">
         <v>314</v>
       </c>
-      <c r="N44" t="s" s="2">
+      <c r="O44" t="s" s="2">
         <v>315</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>316</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>79</v>
@@ -7298,11 +7295,11 @@
         <v>176</v>
       </c>
       <c r="Y44" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="Z44" t="s" s="2">
         <v>317</v>
       </c>
-      <c r="Z44" t="s" s="2">
-        <v>318</v>
-      </c>
       <c r="AA44" t="s" s="2">
         <v>79</v>
       </c>
@@ -7319,7 +7316,7 @@
         <v>79</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7354,10 +7351,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7383,14 +7380,14 @@
         <v>159</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>320</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>321</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>79</v>
@@ -7439,7 +7436,7 @@
         <v>79</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7454,13 +7451,13 @@
         <v>101</v>
       </c>
       <c r="AK45" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="AL45" t="s" s="2">
         <v>323</v>
       </c>
-      <c r="AL45" t="s" s="2">
+      <c r="AM45" t="s" s="2">
         <v>324</v>
-      </c>
-      <c r="AM45" t="s" s="2">
-        <v>325</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>79</v>
@@ -7474,10 +7471,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7500,17 +7497,17 @@
         <v>90</v>
       </c>
       <c r="K46" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="L46" t="s" s="2">
         <v>327</v>
       </c>
-      <c r="L46" t="s" s="2">
+      <c r="M46" t="s" s="2">
         <v>328</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>329</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>79</v>
@@ -7559,7 +7556,7 @@
         <v>79</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>89</v>
@@ -7574,10 +7571,10 @@
         <v>101</v>
       </c>
       <c r="AK46" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="AL46" t="s" s="2">
         <v>331</v>
-      </c>
-      <c r="AL46" t="s" s="2">
-        <v>332</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>79</v>
@@ -7594,10 +7591,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7620,17 +7617,17 @@
         <v>90</v>
       </c>
       <c r="K47" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="L47" t="s" s="2">
         <v>334</v>
       </c>
-      <c r="L47" t="s" s="2">
+      <c r="M47" t="s" s="2">
         <v>335</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>336</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>79</v>
@@ -7679,7 +7676,7 @@
         <v>79</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>89</v>
@@ -7694,10 +7691,10 @@
         <v>101</v>
       </c>
       <c r="AK47" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="AL47" t="s" s="2">
         <v>338</v>
-      </c>
-      <c r="AL47" t="s" s="2">
-        <v>339</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>79</v>
@@ -7714,10 +7711,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7743,16 +7740,16 @@
         <v>147</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="M48" t="s" s="2">
         <v>341</v>
       </c>
-      <c r="M48" t="s" s="2">
+      <c r="N48" t="s" s="2">
         <v>342</v>
       </c>
-      <c r="N48" t="s" s="2">
+      <c r="O48" t="s" s="2">
         <v>343</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>344</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>79</v>
@@ -7801,7 +7798,7 @@
         <v>79</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7816,10 +7813,10 @@
         <v>101</v>
       </c>
       <c r="AK48" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="AL48" t="s" s="2">
         <v>345</v>
-      </c>
-      <c r="AL48" t="s" s="2">
-        <v>346</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>79</v>
@@ -7836,10 +7833,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7862,17 +7859,17 @@
         <v>79</v>
       </c>
       <c r="K49" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="L49" t="s" s="2">
         <v>348</v>
       </c>
-      <c r="L49" t="s" s="2">
+      <c r="M49" t="s" s="2">
         <v>349</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>350</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>79</v>
@@ -7919,7 +7916,7 @@
         <v>152</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -7954,10 +7951,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8072,10 +8069,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8192,14 +8189,14 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -8221,10 +8218,10 @@
         <v>135</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="M52" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>357</v>
       </c>
       <c r="N52" t="s" s="2">
         <v>138</v>
@@ -8279,7 +8276,7 @@
         <v>79</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8314,10 +8311,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8343,14 +8340,14 @@
         <v>147</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="M53" t="s" s="2">
         <v>360</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>361</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>79</v>
@@ -8399,7 +8396,7 @@
         <v>79</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8434,10 +8431,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8463,14 +8460,14 @@
         <v>147</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="M54" t="s" s="2">
         <v>364</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>365</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>79</v>
@@ -8519,7 +8516,7 @@
         <v>79</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8554,10 +8551,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8583,16 +8580,16 @@
         <v>183</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="M55" t="s" s="2">
         <v>367</v>
       </c>
-      <c r="M55" t="s" s="2">
+      <c r="N55" t="s" s="2">
         <v>368</v>
       </c>
-      <c r="N55" t="s" s="2">
+      <c r="O55" t="s" s="2">
         <v>369</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>370</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>79</v>
@@ -8617,14 +8614,14 @@
         <v>79</v>
       </c>
       <c r="X55" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="Y55" t="s" s="2">
         <v>371</v>
       </c>
-      <c r="Y55" t="s" s="2">
+      <c r="Z55" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="Z55" t="s" s="2">
-        <v>373</v>
-      </c>
       <c r="AA55" t="s" s="2">
         <v>79</v>
       </c>
@@ -8641,7 +8638,7 @@
         <v>79</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>89</v>
@@ -8676,10 +8673,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8702,17 +8699,17 @@
         <v>79</v>
       </c>
       <c r="K56" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="L56" t="s" s="2">
         <v>375</v>
       </c>
-      <c r="L56" t="s" s="2">
+      <c r="M56" t="s" s="2">
         <v>376</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>377</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>79</v>
@@ -8761,7 +8758,7 @@
         <v>79</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8796,10 +8793,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8822,17 +8819,17 @@
         <v>79</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="L57" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="M57" t="s" s="2">
         <v>380</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>381</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>79</v>
@@ -8881,7 +8878,7 @@
         <v>79</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -8916,10 +8913,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8942,17 +8939,17 @@
         <v>79</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>384</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>385</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>79</v>
@@ -9001,7 +8998,7 @@
         <v>79</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -9036,10 +9033,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9062,17 +9059,17 @@
         <v>79</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="L59" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="M59" t="s" s="2">
         <v>388</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>389</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>79</v>
@@ -9121,7 +9118,7 @@
         <v>79</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9156,10 +9153,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9182,17 +9179,17 @@
         <v>79</v>
       </c>
       <c r="K60" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="L60" t="s" s="2">
         <v>391</v>
       </c>
-      <c r="L60" t="s" s="2">
+      <c r="M60" t="s" s="2">
         <v>392</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>393</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>79</v>
@@ -9241,7 +9238,7 @@
         <v>79</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9276,10 +9273,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9302,17 +9299,17 @@
         <v>79</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="L61" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="M61" t="s" s="2">
         <v>396</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>397</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>79</v>
@@ -9361,7 +9358,7 @@
         <v>79</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9396,10 +9393,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9422,17 +9419,17 @@
         <v>79</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="L62" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="M62" t="s" s="2">
         <v>399</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>400</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>79</v>
@@ -9481,7 +9478,7 @@
         <v>79</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9516,13 +9513,13 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="C63" t="s" s="2">
         <v>402</v>
-      </c>
-      <c r="B63" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="C63" t="s" s="2">
-        <v>403</v>
       </c>
       <c r="D63" t="s" s="2">
         <v>79</v>
@@ -9544,17 +9541,17 @@
         <v>79</v>
       </c>
       <c r="K63" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="L63" t="s" s="2">
         <v>348</v>
       </c>
-      <c r="L63" t="s" s="2">
+      <c r="M63" t="s" s="2">
         <v>349</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>350</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>79</v>
@@ -9603,7 +9600,7 @@
         <v>79</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9638,10 +9635,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9756,10 +9753,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9876,14 +9873,14 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -9905,10 +9902,10 @@
         <v>135</v>
       </c>
       <c r="L66" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="M66" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>357</v>
       </c>
       <c r="N66" t="s" s="2">
         <v>138</v>
@@ -9963,7 +9960,7 @@
         <v>79</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -9998,10 +9995,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10027,14 +10024,14 @@
         <v>147</v>
       </c>
       <c r="L67" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="M67" t="s" s="2">
         <v>360</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>361</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>79</v>
@@ -10083,7 +10080,7 @@
         <v>79</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10118,10 +10115,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10147,14 +10144,14 @@
         <v>147</v>
       </c>
       <c r="L68" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="M68" t="s" s="2">
         <v>364</v>
-      </c>
-      <c r="M68" t="s" s="2">
-        <v>365</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>79</v>
@@ -10203,7 +10200,7 @@
         <v>79</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10238,10 +10235,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10267,16 +10264,16 @@
         <v>183</v>
       </c>
       <c r="L69" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="M69" t="s" s="2">
         <v>367</v>
       </c>
-      <c r="M69" t="s" s="2">
+      <c r="N69" t="s" s="2">
         <v>368</v>
       </c>
-      <c r="N69" t="s" s="2">
+      <c r="O69" t="s" s="2">
         <v>369</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>370</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>79</v>
@@ -10301,14 +10298,14 @@
         <v>79</v>
       </c>
       <c r="X69" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="Y69" t="s" s="2">
         <v>371</v>
       </c>
-      <c r="Y69" t="s" s="2">
+      <c r="Z69" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="Z69" t="s" s="2">
-        <v>373</v>
-      </c>
       <c r="AA69" t="s" s="2">
         <v>79</v>
       </c>
@@ -10325,7 +10322,7 @@
         <v>79</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>89</v>
@@ -10360,10 +10357,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="B70" t="s" s="2">
         <v>410</v>
-      </c>
-      <c r="B70" t="s" s="2">
-        <v>411</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10478,10 +10475,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="B71" t="s" s="2">
         <v>412</v>
-      </c>
-      <c r="B71" t="s" s="2">
-        <v>413</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10598,10 +10595,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="B72" t="s" s="2">
         <v>414</v>
-      </c>
-      <c r="B72" t="s" s="2">
-        <v>415</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10720,10 +10717,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="B73" t="s" s="2">
         <v>416</v>
-      </c>
-      <c r="B73" t="s" s="2">
-        <v>417</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10768,7 +10765,7 @@
         <v>79</v>
       </c>
       <c r="S73" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="T73" t="s" s="2">
         <v>79</v>
@@ -10822,7 +10819,7 @@
         <v>101</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="AL73" t="s" s="2">
         <v>79</v>
@@ -10842,10 +10839,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10868,17 +10865,17 @@
         <v>79</v>
       </c>
       <c r="K74" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="L74" t="s" s="2">
         <v>375</v>
       </c>
-      <c r="L74" t="s" s="2">
+      <c r="M74" t="s" s="2">
         <v>376</v>
-      </c>
-      <c r="M74" t="s" s="2">
-        <v>377</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>79</v>
@@ -10927,7 +10924,7 @@
         <v>79</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -10962,10 +10959,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10988,17 +10985,17 @@
         <v>79</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="L75" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="M75" t="s" s="2">
         <v>380</v>
-      </c>
-      <c r="M75" t="s" s="2">
-        <v>381</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>79</v>
@@ -11047,7 +11044,7 @@
         <v>79</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -11082,10 +11079,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11108,17 +11105,17 @@
         <v>79</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="L76" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="M76" t="s" s="2">
         <v>384</v>
-      </c>
-      <c r="M76" t="s" s="2">
-        <v>385</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>79</v>
@@ -11167,7 +11164,7 @@
         <v>79</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -11202,10 +11199,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11228,17 +11225,17 @@
         <v>79</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="L77" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="M77" t="s" s="2">
         <v>388</v>
-      </c>
-      <c r="M77" t="s" s="2">
-        <v>389</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>79</v>
@@ -11287,7 +11284,7 @@
         <v>79</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -11322,10 +11319,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11348,17 +11345,17 @@
         <v>79</v>
       </c>
       <c r="K78" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="L78" t="s" s="2">
         <v>391</v>
       </c>
-      <c r="L78" t="s" s="2">
+      <c r="M78" t="s" s="2">
         <v>392</v>
-      </c>
-      <c r="M78" t="s" s="2">
-        <v>393</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>79</v>
@@ -11407,7 +11404,7 @@
         <v>79</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -11442,10 +11439,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11468,17 +11465,17 @@
         <v>79</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="L79" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="M79" t="s" s="2">
         <v>396</v>
-      </c>
-      <c r="M79" t="s" s="2">
-        <v>397</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>79</v>
@@ -11527,7 +11524,7 @@
         <v>79</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -11562,10 +11559,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11588,17 +11585,17 @@
         <v>79</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="L80" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="M80" t="s" s="2">
         <v>399</v>
-      </c>
-      <c r="M80" t="s" s="2">
-        <v>400</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>79</v>
@@ -11647,7 +11644,7 @@
         <v>79</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -11662,10 +11659,10 @@
         <v>101</v>
       </c>
       <c r="AK80" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="AL80" t="s" s="2">
         <v>427</v>
-      </c>
-      <c r="AL80" t="s" s="2">
-        <v>428</v>
       </c>
       <c r="AM80" t="s" s="2">
         <v>79</v>
@@ -11682,13 +11679,13 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="B81" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="C81" t="s" s="2">
         <v>429</v>
-      </c>
-      <c r="B81" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="C81" t="s" s="2">
-        <v>430</v>
       </c>
       <c r="D81" t="s" s="2">
         <v>79</v>
@@ -11710,17 +11707,17 @@
         <v>79</v>
       </c>
       <c r="K81" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="L81" t="s" s="2">
         <v>348</v>
       </c>
-      <c r="L81" t="s" s="2">
+      <c r="M81" t="s" s="2">
         <v>349</v>
-      </c>
-      <c r="M81" t="s" s="2">
-        <v>350</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>79</v>
@@ -11769,7 +11766,7 @@
         <v>79</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -11804,10 +11801,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11922,10 +11919,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12042,14 +12039,14 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
@@ -12071,10 +12068,10 @@
         <v>135</v>
       </c>
       <c r="L84" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="M84" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="M84" t="s" s="2">
-        <v>357</v>
       </c>
       <c r="N84" t="s" s="2">
         <v>138</v>
@@ -12129,7 +12126,7 @@
         <v>79</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12164,10 +12161,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12193,14 +12190,14 @@
         <v>147</v>
       </c>
       <c r="L85" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="M85" t="s" s="2">
         <v>360</v>
-      </c>
-      <c r="M85" t="s" s="2">
-        <v>361</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>79</v>
@@ -12249,7 +12246,7 @@
         <v>79</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12284,10 +12281,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12313,14 +12310,14 @@
         <v>147</v>
       </c>
       <c r="L86" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="M86" t="s" s="2">
         <v>364</v>
-      </c>
-      <c r="M86" t="s" s="2">
-        <v>365</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>79</v>
@@ -12369,7 +12366,7 @@
         <v>79</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -12404,10 +12401,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12433,16 +12430,16 @@
         <v>183</v>
       </c>
       <c r="L87" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="M87" t="s" s="2">
         <v>367</v>
       </c>
-      <c r="M87" t="s" s="2">
+      <c r="N87" t="s" s="2">
         <v>368</v>
       </c>
-      <c r="N87" t="s" s="2">
+      <c r="O87" t="s" s="2">
         <v>369</v>
-      </c>
-      <c r="O87" t="s" s="2">
-        <v>370</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>79</v>
@@ -12467,14 +12464,14 @@
         <v>79</v>
       </c>
       <c r="X87" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="Y87" t="s" s="2">
         <v>371</v>
       </c>
-      <c r="Y87" t="s" s="2">
+      <c r="Z87" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="Z87" t="s" s="2">
-        <v>373</v>
-      </c>
       <c r="AA87" t="s" s="2">
         <v>79</v>
       </c>
@@ -12491,7 +12488,7 @@
         <v>79</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>89</v>
@@ -12526,10 +12523,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12644,10 +12641,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12764,10 +12761,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12886,10 +12883,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12934,7 +12931,7 @@
         <v>79</v>
       </c>
       <c r="S91" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="T91" t="s" s="2">
         <v>79</v>
@@ -12988,7 +12985,7 @@
         <v>101</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="AL91" t="s" s="2">
         <v>79</v>
@@ -13008,10 +13005,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13034,17 +13031,17 @@
         <v>79</v>
       </c>
       <c r="K92" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="L92" t="s" s="2">
         <v>375</v>
       </c>
-      <c r="L92" t="s" s="2">
+      <c r="M92" t="s" s="2">
         <v>376</v>
-      </c>
-      <c r="M92" t="s" s="2">
-        <v>377</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>79</v>
@@ -13093,7 +13090,7 @@
         <v>79</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -13128,10 +13125,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13154,17 +13151,17 @@
         <v>79</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="L93" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="M93" t="s" s="2">
         <v>380</v>
-      </c>
-      <c r="M93" t="s" s="2">
-        <v>381</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>79</v>
@@ -13213,7 +13210,7 @@
         <v>79</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -13248,10 +13245,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13274,17 +13271,17 @@
         <v>79</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="L94" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="M94" t="s" s="2">
         <v>384</v>
-      </c>
-      <c r="M94" t="s" s="2">
-        <v>385</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>79</v>
@@ -13333,7 +13330,7 @@
         <v>79</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -13368,10 +13365,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13394,17 +13391,17 @@
         <v>79</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="L95" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="M95" t="s" s="2">
         <v>388</v>
-      </c>
-      <c r="M95" t="s" s="2">
-        <v>389</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>79</v>
@@ -13453,7 +13450,7 @@
         <v>79</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -13488,10 +13485,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13514,17 +13511,17 @@
         <v>79</v>
       </c>
       <c r="K96" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="L96" t="s" s="2">
         <v>391</v>
       </c>
-      <c r="L96" t="s" s="2">
+      <c r="M96" t="s" s="2">
         <v>392</v>
-      </c>
-      <c r="M96" t="s" s="2">
-        <v>393</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>79</v>
@@ -13573,7 +13570,7 @@
         <v>79</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
@@ -13608,10 +13605,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13634,17 +13631,17 @@
         <v>79</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="L97" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="M97" t="s" s="2">
         <v>396</v>
-      </c>
-      <c r="M97" t="s" s="2">
-        <v>397</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>79</v>
@@ -13693,7 +13690,7 @@
         <v>79</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -13728,10 +13725,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13754,17 +13751,17 @@
         <v>79</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="L98" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="M98" t="s" s="2">
         <v>399</v>
-      </c>
-      <c r="M98" t="s" s="2">
-        <v>400</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>79</v>
@@ -13813,7 +13810,7 @@
         <v>79</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
@@ -13828,10 +13825,10 @@
         <v>101</v>
       </c>
       <c r="AK98" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="AL98" t="s" s="2">
         <v>450</v>
-      </c>
-      <c r="AL98" t="s" s="2">
-        <v>451</v>
       </c>
       <c r="AM98" t="s" s="2">
         <v>79</v>
@@ -13848,13 +13845,13 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="B99" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="C99" t="s" s="2">
         <v>452</v>
-      </c>
-      <c r="B99" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="C99" t="s" s="2">
-        <v>453</v>
       </c>
       <c r="D99" t="s" s="2">
         <v>79</v>
@@ -13876,17 +13873,17 @@
         <v>79</v>
       </c>
       <c r="K99" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="L99" t="s" s="2">
         <v>348</v>
       </c>
-      <c r="L99" t="s" s="2">
+      <c r="M99" t="s" s="2">
         <v>349</v>
-      </c>
-      <c r="M99" t="s" s="2">
-        <v>350</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>79</v>
@@ -13935,7 +13932,7 @@
         <v>79</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
@@ -13970,10 +13967,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14088,10 +14085,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14208,14 +14205,14 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E102" s="2"/>
       <c r="F102" t="s" s="2">
@@ -14237,10 +14234,10 @@
         <v>135</v>
       </c>
       <c r="L102" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="M102" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="M102" t="s" s="2">
-        <v>357</v>
       </c>
       <c r="N102" t="s" s="2">
         <v>138</v>
@@ -14295,7 +14292,7 @@
         <v>79</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -14330,10 +14327,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14359,14 +14356,14 @@
         <v>147</v>
       </c>
       <c r="L103" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="M103" t="s" s="2">
         <v>360</v>
-      </c>
-      <c r="M103" t="s" s="2">
-        <v>361</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>79</v>
@@ -14415,7 +14412,7 @@
         <v>79</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -14450,10 +14447,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14479,14 +14476,14 @@
         <v>147</v>
       </c>
       <c r="L104" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="M104" t="s" s="2">
         <v>364</v>
-      </c>
-      <c r="M104" t="s" s="2">
-        <v>365</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>79</v>
@@ -14535,7 +14532,7 @@
         <v>79</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
@@ -14570,10 +14567,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14599,16 +14596,16 @@
         <v>183</v>
       </c>
       <c r="L105" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="M105" t="s" s="2">
         <v>367</v>
       </c>
-      <c r="M105" t="s" s="2">
+      <c r="N105" t="s" s="2">
         <v>368</v>
       </c>
-      <c r="N105" t="s" s="2">
+      <c r="O105" t="s" s="2">
         <v>369</v>
-      </c>
-      <c r="O105" t="s" s="2">
-        <v>370</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>79</v>
@@ -14633,14 +14630,14 @@
         <v>79</v>
       </c>
       <c r="X105" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="Y105" t="s" s="2">
         <v>371</v>
       </c>
-      <c r="Y105" t="s" s="2">
+      <c r="Z105" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="Z105" t="s" s="2">
-        <v>373</v>
-      </c>
       <c r="AA105" t="s" s="2">
         <v>79</v>
       </c>
@@ -14657,7 +14654,7 @@
         <v>79</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>89</v>
@@ -14692,10 +14689,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14810,10 +14807,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14930,10 +14927,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15052,10 +15049,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15100,7 +15097,7 @@
         <v>79</v>
       </c>
       <c r="S109" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="T109" t="s" s="2">
         <v>79</v>
@@ -15154,7 +15151,7 @@
         <v>101</v>
       </c>
       <c r="AK109" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="AL109" t="s" s="2">
         <v>79</v>
@@ -15174,10 +15171,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15200,17 +15197,17 @@
         <v>79</v>
       </c>
       <c r="K110" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="L110" t="s" s="2">
         <v>375</v>
       </c>
-      <c r="L110" t="s" s="2">
+      <c r="M110" t="s" s="2">
         <v>376</v>
-      </c>
-      <c r="M110" t="s" s="2">
-        <v>377</v>
       </c>
       <c r="N110" s="2"/>
       <c r="O110" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>79</v>
@@ -15259,7 +15256,7 @@
         <v>79</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
@@ -15294,10 +15291,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15320,17 +15317,17 @@
         <v>79</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="L111" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="M111" t="s" s="2">
         <v>380</v>
-      </c>
-      <c r="M111" t="s" s="2">
-        <v>381</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>79</v>
@@ -15379,7 +15376,7 @@
         <v>79</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
@@ -15414,10 +15411,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15440,17 +15437,17 @@
         <v>79</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="L112" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="M112" t="s" s="2">
         <v>384</v>
-      </c>
-      <c r="M112" t="s" s="2">
-        <v>385</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="P112" t="s" s="2">
         <v>79</v>
@@ -15499,7 +15496,7 @@
         <v>79</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>80</v>
@@ -15534,10 +15531,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15560,17 +15557,17 @@
         <v>79</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="L113" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="M113" t="s" s="2">
         <v>388</v>
-      </c>
-      <c r="M113" t="s" s="2">
-        <v>389</v>
       </c>
       <c r="N113" s="2"/>
       <c r="O113" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>79</v>
@@ -15619,7 +15616,7 @@
         <v>79</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>80</v>
@@ -15654,10 +15651,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15680,17 +15677,17 @@
         <v>79</v>
       </c>
       <c r="K114" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="L114" t="s" s="2">
         <v>391</v>
       </c>
-      <c r="L114" t="s" s="2">
+      <c r="M114" t="s" s="2">
         <v>392</v>
-      </c>
-      <c r="M114" t="s" s="2">
-        <v>393</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>79</v>
@@ -15739,7 +15736,7 @@
         <v>79</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>80</v>
@@ -15774,10 +15771,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -15800,17 +15797,17 @@
         <v>79</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="L115" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="M115" t="s" s="2">
         <v>396</v>
-      </c>
-      <c r="M115" t="s" s="2">
-        <v>397</v>
       </c>
       <c r="N115" s="2"/>
       <c r="O115" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>79</v>
@@ -15859,7 +15856,7 @@
         <v>79</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>80</v>
@@ -15894,10 +15891,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -15920,17 +15917,17 @@
         <v>79</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="L116" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="M116" t="s" s="2">
         <v>399</v>
-      </c>
-      <c r="M116" t="s" s="2">
-        <v>400</v>
       </c>
       <c r="N116" s="2"/>
       <c r="O116" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="P116" t="s" s="2">
         <v>79</v>
@@ -15979,7 +15976,7 @@
         <v>79</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>80</v>
@@ -15994,10 +15991,10 @@
         <v>101</v>
       </c>
       <c r="AK116" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="AL116" t="s" s="2">
         <v>473</v>
-      </c>
-      <c r="AL116" t="s" s="2">
-        <v>474</v>
       </c>
       <c r="AM116" t="s" s="2">
         <v>79</v>
@@ -16014,13 +16011,13 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="B117" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="C117" t="s" s="2">
         <v>475</v>
-      </c>
-      <c r="B117" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="C117" t="s" s="2">
-        <v>476</v>
       </c>
       <c r="D117" t="s" s="2">
         <v>79</v>
@@ -16042,17 +16039,17 @@
         <v>79</v>
       </c>
       <c r="K117" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="L117" t="s" s="2">
         <v>348</v>
       </c>
-      <c r="L117" t="s" s="2">
+      <c r="M117" t="s" s="2">
         <v>349</v>
-      </c>
-      <c r="M117" t="s" s="2">
-        <v>350</v>
       </c>
       <c r="N117" s="2"/>
       <c r="O117" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="P117" t="s" s="2">
         <v>79</v>
@@ -16101,7 +16098,7 @@
         <v>79</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>80</v>
@@ -16136,10 +16133,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16254,10 +16251,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16374,14 +16371,14 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E120" s="2"/>
       <c r="F120" t="s" s="2">
@@ -16403,10 +16400,10 @@
         <v>135</v>
       </c>
       <c r="L120" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="M120" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="M120" t="s" s="2">
-        <v>357</v>
       </c>
       <c r="N120" t="s" s="2">
         <v>138</v>
@@ -16461,7 +16458,7 @@
         <v>79</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>80</v>
@@ -16496,10 +16493,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16525,14 +16522,14 @@
         <v>147</v>
       </c>
       <c r="L121" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="M121" t="s" s="2">
         <v>360</v>
-      </c>
-      <c r="M121" t="s" s="2">
-        <v>361</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="P121" t="s" s="2">
         <v>79</v>
@@ -16581,7 +16578,7 @@
         <v>79</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>80</v>
@@ -16616,10 +16613,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -16645,14 +16642,14 @@
         <v>147</v>
       </c>
       <c r="L122" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="M122" t="s" s="2">
         <v>364</v>
-      </c>
-      <c r="M122" t="s" s="2">
-        <v>365</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="P122" t="s" s="2">
         <v>79</v>
@@ -16701,7 +16698,7 @@
         <v>79</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>80</v>
@@ -16736,10 +16733,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -16765,16 +16762,16 @@
         <v>183</v>
       </c>
       <c r="L123" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="M123" t="s" s="2">
         <v>367</v>
       </c>
-      <c r="M123" t="s" s="2">
+      <c r="N123" t="s" s="2">
         <v>368</v>
       </c>
-      <c r="N123" t="s" s="2">
+      <c r="O123" t="s" s="2">
         <v>369</v>
-      </c>
-      <c r="O123" t="s" s="2">
-        <v>370</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>79</v>
@@ -16799,14 +16796,14 @@
         <v>79</v>
       </c>
       <c r="X123" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="Y123" t="s" s="2">
         <v>371</v>
       </c>
-      <c r="Y123" t="s" s="2">
+      <c r="Z123" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="Z123" t="s" s="2">
-        <v>373</v>
-      </c>
       <c r="AA123" t="s" s="2">
         <v>79</v>
       </c>
@@ -16823,7 +16820,7 @@
         <v>79</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>89</v>
@@ -16858,10 +16855,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -16976,10 +16973,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17096,10 +17093,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17218,10 +17215,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17266,7 +17263,7 @@
         <v>79</v>
       </c>
       <c r="S127" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="T127" t="s" s="2">
         <v>79</v>
@@ -17320,7 +17317,7 @@
         <v>101</v>
       </c>
       <c r="AK127" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="AL127" t="s" s="2">
         <v>79</v>
@@ -17340,10 +17337,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17366,17 +17363,17 @@
         <v>79</v>
       </c>
       <c r="K128" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="L128" t="s" s="2">
         <v>375</v>
       </c>
-      <c r="L128" t="s" s="2">
+      <c r="M128" t="s" s="2">
         <v>376</v>
-      </c>
-      <c r="M128" t="s" s="2">
-        <v>377</v>
       </c>
       <c r="N128" s="2"/>
       <c r="O128" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="P128" t="s" s="2">
         <v>79</v>
@@ -17425,7 +17422,7 @@
         <v>79</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>80</v>
@@ -17460,10 +17457,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -17486,17 +17483,17 @@
         <v>79</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="L129" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="M129" t="s" s="2">
         <v>380</v>
-      </c>
-      <c r="M129" t="s" s="2">
-        <v>381</v>
       </c>
       <c r="N129" s="2"/>
       <c r="O129" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="P129" t="s" s="2">
         <v>79</v>
@@ -17545,7 +17542,7 @@
         <v>79</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>80</v>
@@ -17580,10 +17577,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -17606,17 +17603,17 @@
         <v>79</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="L130" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="M130" t="s" s="2">
         <v>384</v>
-      </c>
-      <c r="M130" t="s" s="2">
-        <v>385</v>
       </c>
       <c r="N130" s="2"/>
       <c r="O130" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="P130" t="s" s="2">
         <v>79</v>
@@ -17665,7 +17662,7 @@
         <v>79</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>80</v>
@@ -17700,10 +17697,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -17726,17 +17723,17 @@
         <v>79</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="L131" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="M131" t="s" s="2">
         <v>388</v>
-      </c>
-      <c r="M131" t="s" s="2">
-        <v>389</v>
       </c>
       <c r="N131" s="2"/>
       <c r="O131" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="P131" t="s" s="2">
         <v>79</v>
@@ -17785,7 +17782,7 @@
         <v>79</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>80</v>
@@ -17820,10 +17817,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -17846,17 +17843,17 @@
         <v>79</v>
       </c>
       <c r="K132" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="L132" t="s" s="2">
         <v>391</v>
       </c>
-      <c r="L132" t="s" s="2">
+      <c r="M132" t="s" s="2">
         <v>392</v>
-      </c>
-      <c r="M132" t="s" s="2">
-        <v>393</v>
       </c>
       <c r="N132" s="2"/>
       <c r="O132" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="P132" t="s" s="2">
         <v>79</v>
@@ -17905,7 +17902,7 @@
         <v>79</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>80</v>
@@ -17940,10 +17937,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -17966,17 +17963,17 @@
         <v>79</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="L133" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="M133" t="s" s="2">
         <v>396</v>
-      </c>
-      <c r="M133" t="s" s="2">
-        <v>397</v>
       </c>
       <c r="N133" s="2"/>
       <c r="O133" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="P133" t="s" s="2">
         <v>79</v>
@@ -18025,7 +18022,7 @@
         <v>79</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>80</v>
@@ -18060,10 +18057,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -18086,17 +18083,17 @@
         <v>79</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="L134" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="M134" t="s" s="2">
         <v>399</v>
-      </c>
-      <c r="M134" t="s" s="2">
-        <v>400</v>
       </c>
       <c r="N134" s="2"/>
       <c r="O134" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="P134" t="s" s="2">
         <v>79</v>
@@ -18145,7 +18142,7 @@
         <v>79</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>80</v>
@@ -18160,10 +18157,10 @@
         <v>101</v>
       </c>
       <c r="AK134" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="AL134" t="s" s="2">
         <v>496</v>
-      </c>
-      <c r="AL134" t="s" s="2">
-        <v>497</v>
       </c>
       <c r="AM134" t="s" s="2">
         <v>79</v>
@@ -18180,13 +18177,13 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="B135" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="C135" t="s" s="2">
         <v>498</v>
-      </c>
-      <c r="B135" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="C135" t="s" s="2">
-        <v>499</v>
       </c>
       <c r="D135" t="s" s="2">
         <v>79</v>
@@ -18208,17 +18205,17 @@
         <v>79</v>
       </c>
       <c r="K135" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="L135" t="s" s="2">
         <v>348</v>
       </c>
-      <c r="L135" t="s" s="2">
+      <c r="M135" t="s" s="2">
         <v>349</v>
-      </c>
-      <c r="M135" t="s" s="2">
-        <v>350</v>
       </c>
       <c r="N135" s="2"/>
       <c r="O135" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="P135" t="s" s="2">
         <v>79</v>
@@ -18267,7 +18264,7 @@
         <v>79</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>80</v>
@@ -18302,10 +18299,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -18420,10 +18417,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -18540,14 +18537,14 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E138" s="2"/>
       <c r="F138" t="s" s="2">
@@ -18569,10 +18566,10 @@
         <v>135</v>
       </c>
       <c r="L138" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="M138" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="M138" t="s" s="2">
-        <v>357</v>
       </c>
       <c r="N138" t="s" s="2">
         <v>138</v>
@@ -18627,7 +18624,7 @@
         <v>79</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>80</v>
@@ -18662,10 +18659,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -18691,14 +18688,14 @@
         <v>147</v>
       </c>
       <c r="L139" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="M139" t="s" s="2">
         <v>360</v>
-      </c>
-      <c r="M139" t="s" s="2">
-        <v>361</v>
       </c>
       <c r="N139" s="2"/>
       <c r="O139" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="P139" t="s" s="2">
         <v>79</v>
@@ -18747,7 +18744,7 @@
         <v>79</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>80</v>
@@ -18782,10 +18779,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -18811,14 +18808,14 @@
         <v>147</v>
       </c>
       <c r="L140" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="M140" t="s" s="2">
         <v>364</v>
-      </c>
-      <c r="M140" t="s" s="2">
-        <v>365</v>
       </c>
       <c r="N140" s="2"/>
       <c r="O140" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="P140" t="s" s="2">
         <v>79</v>
@@ -18867,7 +18864,7 @@
         <v>79</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>80</v>
@@ -18902,10 +18899,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -18931,16 +18928,16 @@
         <v>183</v>
       </c>
       <c r="L141" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="M141" t="s" s="2">
         <v>367</v>
       </c>
-      <c r="M141" t="s" s="2">
+      <c r="N141" t="s" s="2">
         <v>368</v>
       </c>
-      <c r="N141" t="s" s="2">
+      <c r="O141" t="s" s="2">
         <v>369</v>
-      </c>
-      <c r="O141" t="s" s="2">
-        <v>370</v>
       </c>
       <c r="P141" t="s" s="2">
         <v>79</v>
@@ -18965,14 +18962,14 @@
         <v>79</v>
       </c>
       <c r="X141" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="Y141" t="s" s="2">
         <v>371</v>
       </c>
-      <c r="Y141" t="s" s="2">
+      <c r="Z141" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="Z141" t="s" s="2">
-        <v>373</v>
-      </c>
       <c r="AA141" t="s" s="2">
         <v>79</v>
       </c>
@@ -18989,7 +18986,7 @@
         <v>79</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>89</v>
@@ -19024,10 +19021,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -19142,10 +19139,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -19262,10 +19259,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -19384,10 +19381,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -19432,7 +19429,7 @@
         <v>79</v>
       </c>
       <c r="S145" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="T145" t="s" s="2">
         <v>79</v>
@@ -19486,7 +19483,7 @@
         <v>101</v>
       </c>
       <c r="AK145" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="AL145" t="s" s="2">
         <v>79</v>
@@ -19506,10 +19503,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -19532,17 +19529,17 @@
         <v>79</v>
       </c>
       <c r="K146" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="L146" t="s" s="2">
         <v>375</v>
       </c>
-      <c r="L146" t="s" s="2">
+      <c r="M146" t="s" s="2">
         <v>376</v>
-      </c>
-      <c r="M146" t="s" s="2">
-        <v>377</v>
       </c>
       <c r="N146" s="2"/>
       <c r="O146" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="P146" t="s" s="2">
         <v>79</v>
@@ -19591,7 +19588,7 @@
         <v>79</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>80</v>
@@ -19626,10 +19623,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -19652,17 +19649,17 @@
         <v>79</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="L147" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="M147" t="s" s="2">
         <v>380</v>
-      </c>
-      <c r="M147" t="s" s="2">
-        <v>381</v>
       </c>
       <c r="N147" s="2"/>
       <c r="O147" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="P147" t="s" s="2">
         <v>79</v>
@@ -19711,7 +19708,7 @@
         <v>79</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>80</v>
@@ -19746,10 +19743,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -19772,17 +19769,17 @@
         <v>79</v>
       </c>
       <c r="K148" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="L148" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="M148" t="s" s="2">
         <v>384</v>
-      </c>
-      <c r="M148" t="s" s="2">
-        <v>385</v>
       </c>
       <c r="N148" s="2"/>
       <c r="O148" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="P148" t="s" s="2">
         <v>79</v>
@@ -19831,7 +19828,7 @@
         <v>79</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>80</v>
@@ -19866,10 +19863,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -19892,17 +19889,17 @@
         <v>79</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="L149" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="M149" t="s" s="2">
         <v>388</v>
-      </c>
-      <c r="M149" t="s" s="2">
-        <v>389</v>
       </c>
       <c r="N149" s="2"/>
       <c r="O149" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="P149" t="s" s="2">
         <v>79</v>
@@ -19951,7 +19948,7 @@
         <v>79</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>80</v>
@@ -19986,10 +19983,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -20012,17 +20009,17 @@
         <v>79</v>
       </c>
       <c r="K150" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="L150" t="s" s="2">
         <v>391</v>
       </c>
-      <c r="L150" t="s" s="2">
+      <c r="M150" t="s" s="2">
         <v>392</v>
-      </c>
-      <c r="M150" t="s" s="2">
-        <v>393</v>
       </c>
       <c r="N150" s="2"/>
       <c r="O150" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="P150" t="s" s="2">
         <v>79</v>
@@ -20071,7 +20068,7 @@
         <v>79</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>80</v>
@@ -20106,10 +20103,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -20132,17 +20129,17 @@
         <v>79</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="L151" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="M151" t="s" s="2">
         <v>396</v>
-      </c>
-      <c r="M151" t="s" s="2">
-        <v>397</v>
       </c>
       <c r="N151" s="2"/>
       <c r="O151" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="P151" t="s" s="2">
         <v>79</v>
@@ -20191,7 +20188,7 @@
         <v>79</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>80</v>
@@ -20226,10 +20223,10 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -20252,17 +20249,17 @@
         <v>79</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="L152" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="M152" t="s" s="2">
         <v>399</v>
-      </c>
-      <c r="M152" t="s" s="2">
-        <v>400</v>
       </c>
       <c r="N152" s="2"/>
       <c r="O152" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="P152" t="s" s="2">
         <v>79</v>
@@ -20311,7 +20308,7 @@
         <v>79</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>80</v>
@@ -20326,10 +20323,10 @@
         <v>101</v>
       </c>
       <c r="AK152" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="AL152" t="s" s="2">
         <v>519</v>
-      </c>
-      <c r="AL152" t="s" s="2">
-        <v>520</v>
       </c>
       <c r="AM152" t="s" s="2">
         <v>79</v>
@@ -20346,10 +20343,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -20375,16 +20372,16 @@
         <v>183</v>
       </c>
       <c r="L153" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="M153" t="s" s="2">
         <v>522</v>
       </c>
-      <c r="M153" t="s" s="2">
+      <c r="N153" t="s" s="2">
         <v>523</v>
       </c>
-      <c r="N153" t="s" s="2">
+      <c r="O153" t="s" s="2">
         <v>524</v>
-      </c>
-      <c r="O153" t="s" s="2">
-        <v>525</v>
       </c>
       <c r="P153" t="s" s="2">
         <v>79</v>
@@ -20409,14 +20406,14 @@
         <v>79</v>
       </c>
       <c r="X153" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="Y153" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="Z153" t="s" s="2">
         <v>526</v>
       </c>
-      <c r="Z153" t="s" s="2">
-        <v>527</v>
-      </c>
       <c r="AA153" t="s" s="2">
         <v>79</v>
       </c>
@@ -20433,7 +20430,7 @@
         <v>79</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>80</v>
@@ -20468,10 +20465,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -20494,17 +20491,17 @@
         <v>79</v>
       </c>
       <c r="K154" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="L154" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="M154" t="s" s="2">
         <v>529</v>
-      </c>
-      <c r="M154" t="s" s="2">
-        <v>530</v>
       </c>
       <c r="N154" s="2"/>
       <c r="O154" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="P154" t="s" s="2">
         <v>79</v>
@@ -20553,7 +20550,7 @@
         <v>79</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>80</v>
@@ -20588,10 +20585,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -20706,10 +20703,10 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -20826,14 +20823,14 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E157" s="2"/>
       <c r="F157" t="s" s="2">
@@ -20855,10 +20852,10 @@
         <v>135</v>
       </c>
       <c r="L157" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="M157" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="M157" t="s" s="2">
-        <v>357</v>
       </c>
       <c r="N157" t="s" s="2">
         <v>138</v>
@@ -20913,7 +20910,7 @@
         <v>79</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>80</v>
@@ -20948,10 +20945,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -20977,14 +20974,14 @@
         <v>109</v>
       </c>
       <c r="L158" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="M158" t="s" s="2">
         <v>536</v>
-      </c>
-      <c r="M158" t="s" s="2">
-        <v>537</v>
       </c>
       <c r="N158" s="2"/>
       <c r="O158" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="P158" t="s" s="2">
         <v>79</v>
@@ -21012,11 +21009,11 @@
         <v>176</v>
       </c>
       <c r="Y158" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="Z158" t="s" s="2">
         <v>539</v>
       </c>
-      <c r="Z158" t="s" s="2">
-        <v>540</v>
-      </c>
       <c r="AA158" t="s" s="2">
         <v>79</v>
       </c>
@@ -21033,7 +21030,7 @@
         <v>79</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>80</v>
@@ -21068,10 +21065,10 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -21097,14 +21094,14 @@
         <v>159</v>
       </c>
       <c r="L159" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="M159" t="s" s="2">
         <v>542</v>
-      </c>
-      <c r="M159" t="s" s="2">
-        <v>543</v>
       </c>
       <c r="N159" s="2"/>
       <c r="O159" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="P159" t="s" s="2">
         <v>79</v>
@@ -21153,7 +21150,7 @@
         <v>79</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>80</v>
@@ -21180,7 +21177,7 @@
         <v>79</v>
       </c>
       <c r="AO159" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="AP159" t="s" s="2">
         <v>79</v>

--- a/docs/StructureDefinition-DebtPortalPayments.xlsx
+++ b/docs/StructureDefinition-DebtPortalPayments.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.397</t>
+    <t>0.68.401</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-10T10:13:24+00:00</t>
+    <t>2024-11-13T21:40:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalPayments.xlsx
+++ b/docs/StructureDefinition-DebtPortalPayments.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.419</t>
+    <t>0.68.424</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-25T07:50:24+00:00</t>
+    <t>2024-11-30T14:03:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalPayments.xlsx
+++ b/docs/StructureDefinition-DebtPortalPayments.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.424</t>
+    <t>0.68.425</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T14:03:16+00:00</t>
+    <t>2024-11-30T15:07:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalPayments.xlsx
+++ b/docs/StructureDefinition-DebtPortalPayments.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.425</t>
+    <t>0.69.436</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T15:07:22+00:00</t>
+    <t>2024-12-04T11:34:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalPayments.xlsx
+++ b/docs/StructureDefinition-DebtPortalPayments.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.436</t>
+    <t>0.69.437</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T11:34:53+00:00</t>
+    <t>2024-12-04T16:25:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalPayments.xlsx
+++ b/docs/StructureDefinition-DebtPortalPayments.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.437</t>
+    <t>0.69.438</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T16:25:11+00:00</t>
+    <t>2024-12-06T17:18:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalPayments.xlsx
+++ b/docs/StructureDefinition-DebtPortalPayments.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.438</t>
+    <t>0.69.439</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-06T17:18:58+00:00</t>
+    <t>2024-12-07T11:18:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalPayments.xlsx
+++ b/docs/StructureDefinition-DebtPortalPayments.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.439</t>
+    <t>0.69.440</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-07T11:18:15+00:00</t>
+    <t>2024-12-08T09:28:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalPayments.xlsx
+++ b/docs/StructureDefinition-DebtPortalPayments.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.442</t>
+    <t>0.69.448</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-11T20:06:32+00:00</t>
+    <t>2024-12-21T10:24:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file AR TRANSACTION (433) to PaymentReconciliation</t>
+    <t>This StructureDefinition contains the maps for VistA file AR TRANSACTION (433) to PaymentReconciliation.</t>
   </si>
   <si>
     <t>Purpose</t>
